--- a/data/output/2025/evaluasi_19.xlsx
+++ b/data/output/2025/evaluasi_19.xlsx
@@ -14,6 +14,7 @@
     <sheet name="1901" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="1906" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="1902" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="1905" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1149,7 +1150,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1237,6 +1238,230 @@
       <c r="F3" t="inlineStr">
         <is>
           <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1903</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Bangka Barat</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-2.605941399713954</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1903</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Bangka Barat</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0.9832674561193846</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pkrt_q4-25_prov vs q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1903</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Bangka Barat</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>2.462250954348878</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1903</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Bangka Barat</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>35.02711384856159</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1903</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Bangka Barat</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-1.202498261889773</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>1903</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Bangka Barat</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>3.297022601281125</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1903</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Bangka Barat</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>1.444547051064354</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q4-25_prov vs implisit_q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>1903</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Bangka Barat</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>1.346494864223597</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q4-25_prov vs implisit_q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -1251,7 +1476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1395,6 +1620,286 @@
       <c r="F5" t="inlineStr">
         <is>
           <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1971</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kota Pangkalpinang</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-0.06258440492450268</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1971</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kota Pangkalpinang</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0.90835355870635</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>q-to-q_pkrt_q4-25_prov vs q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1971</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kota Pangkalpinang</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>5.598696510793845</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>1971</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kota Pangkalpinang</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>37.52459061488534</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1971</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kota Pangkalpinang</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>-0.5226512063476952</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>1971</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kota Pangkalpinang</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>0.2414607302379907</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1971</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kota Pangkalpinang</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>3.777055407325902</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>1971</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kota Pangkalpinang</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>0.2346408963343412</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q4-25_prov vs implisit_q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>1971</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kota Pangkalpinang</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>0.8422940997004941</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q4-25_prov vs implisit_q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>1971</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kota Pangkalpinang</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>1.144368711984616</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pklnprt_2025_prov vs implisit_y-on-y_pklnprt_2025_kab</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -1409,7 +1914,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1595,20 +2100,20 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>q3-25</t>
+          <t>q4-25</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-4.600767759134969</v>
+        <v>-6.329260884993457</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>sog_q_pi_q4-25</t>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>SoG PI lebih dari +-2 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -1623,18 +2128,242 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>q3-25</t>
+          <t>q4-25</t>
         </is>
       </c>
       <c r="D8" t="n">
+        <v>0.60821225221004</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>q-to-q_pkrt_q4-25_prov vs q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>1904</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Bangka Tengah</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>8.300000000000004</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1904</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Bangka Tengah</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>33.92544194355694</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>1904</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Bangka Tengah</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>-0.02177141857078087</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1904</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Bangka Tengah</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>4.86084689876799</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>1904</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Bangka Tengah</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>0.1796399999999672</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q4-25_prov vs implisit_q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>1904</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kabupaten Bangka Tengah</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>0.9249674980557531</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q4-25_prov vs implisit_q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>1904</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kabupaten Bangka Tengah</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>-4.600767759134969</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>sog_q_pi_q4-25</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>1904</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Kabupaten Bangka Tengah</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
         <v>2.03532514154898</v>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>sog_y-on-y_pi_2025</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>SoG PI lebih dari +-2 persen</t>
         </is>
@@ -1651,7 +2380,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1921,20 +2650,20 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>q3-25</t>
+          <t>q4-25</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2.174363064295648</v>
+        <v>-4.405420406667684</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>sog_y-on-y_pi_q4-25</t>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>SoG PI lebih dari +-2 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -1949,18 +2678,270 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>q3-25</t>
+          <t>q4-25</t>
         </is>
       </c>
       <c r="D11" t="n">
+        <v>0.597551159526382</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>q-to-q_pkrt_q4-25_prov vs q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1901</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Bangka</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>4.153468482709054</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>1901</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Bangka</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>31.48597786644657</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>1901</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kabupaten Bangka</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>7.249089614553236</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>1901</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kabupaten Bangka</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>-0.08952817191175309</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>1901</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Kabupaten Bangka</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>5.908458511132848</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>1901</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Kabupaten Bangka</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>0.5182721260305201</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q4-25_prov vs implisit_q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>1901</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Kabupaten Bangka</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>0.9666452663339762</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pklnprt_2025_prov vs implisit_y-on-y_pklnprt_2025_kab</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>1901</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Kabupaten Bangka</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>2.174363064295648</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>sog_y-on-y_pi_q4-25</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>1901</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Kabupaten Bangka</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
         <v>2.217871231449955</v>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>sog_y-on-y_pi_2025</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>SoG PI lebih dari +-2 persen</t>
         </is>
@@ -1977,7 +2958,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2191,20 +3172,20 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>q3-25</t>
+          <t>q4-25</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2.633007845801729</v>
+        <v>1.369985305597288</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>sog_q_pi_q4-25</t>
+          <t>q-to-q_pkrt_q4-25_prov vs q-to-q_pkrt_q4-25_kab</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>SoG PI lebih dari +-2 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -2219,18 +3200,186 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>q3-25</t>
+          <t>q4-25</t>
         </is>
       </c>
       <c r="D9" t="n">
+        <v>5.110000018079154</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1906</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Belitung Timur</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>-11.20231239448942</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>1906</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Belitung Timur</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>3.689234273229894</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1906</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Belitung Timur</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>0.1241888913036324</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q4-25_prov vs implisit_q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>1906</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Belitung Timur</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>0.59765578082912</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q4-25_prov vs implisit_q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>1906</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kabupaten Belitung Timur</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>2.633007845801729</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>sog_q_pi_q4-25</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>1906</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kabupaten Belitung Timur</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
         <v>2.140311256332587</v>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>sog_y-on-y_pi_q4-25</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>SoG PI lebih dari +-2 persen</t>
         </is>
@@ -2247,7 +3396,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2310,6 +3459,556 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1902</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Belitung</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-0.1259410335165058</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1902</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Belitung</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0.2530210202910909</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pkrt_q4-25_prov vs q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1902</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Belitung</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>3.789000238623072</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1902</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Belitung</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>50.22949104848963</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1902</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Belitung</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>5.304439332300517</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1902</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Belitung</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>1.819362569698558</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>1902</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Belitung</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>5.015352918219238</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1902</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Belitung</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>2.257912465692225</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q4-25_prov vs implisit_q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>1902</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Belitung</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>0.3958979771304573</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q4-25_prov vs implisit_q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1905</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Bangka Selatan</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>-2.77081092267158</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1905</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Bangka Selatan</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>1.208234566013051</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pkrt_q4-25_prov vs q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1905</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Bangka Selatan</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>8.804762413396835</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1905</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Bangka Selatan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>35.9047490176179</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1905</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Bangka Selatan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-2.353218659075491</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1905</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Bangka Selatan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>3.508462467460659</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1905</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Bangka Selatan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0.1241888913037396</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q4-25_prov vs implisit_q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>1905</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Bangka Selatan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0.6902521319856959</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q4-25_prov vs implisit_q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1905</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Bangka Selatan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>2.885672887600753</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_q4-25_prov vs implisit_y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
